--- a/output/_temp/etapa_3_clasificacion/Cierre de OT Turno 16.04 al 22.04.xlsx
+++ b/output/_temp/etapa_3_clasificacion/Cierre de OT Turno 16.04 al 22.04.xlsx
@@ -2423,11 +2423,7 @@
         <f>IF(H7="TT","TRABAJO TERMINADO",IF(H7="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
+      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="7">
         <f>IF(B7="", G7, IF(G7="", LEFT(B7,45), IF(45-LEN(G7)-2&lt;=0, G7, LEFT(B7,45-LEN(G7)-2)&amp;", "&amp;G7)))</f>
         <v/>

--- a/output/_temp/etapa_3_clasificacion/Cierre de OT Turno 16.04 al 22.04.xlsx
+++ b/output/_temp/etapa_3_clasificacion/Cierre de OT Turno 16.04 al 22.04.xlsx
@@ -2219,7 +2219,11 @@
         <f>IF(H3="TT","TRABAJO TERMINADO",IF(H3="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I3" s="7">
         <f>IF(B3="", G3, IF(G3="", LEFT(B3,45), IF(45-LEN(G3)-2&lt;=0, G3, LEFT(B3,45-LEN(G3)-2)&amp;", "&amp;G3)))</f>
         <v/>
@@ -2270,7 +2274,11 @@
         <f>IF(H4="TT","TRABAJO TERMINADO",IF(H4="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I4" s="7">
         <f>IF(B4="", G4, IF(G4="", LEFT(B4,45), IF(45-LEN(G4)-2&lt;=0, G4, LEFT(B4,45-LEN(G4)-2)&amp;", "&amp;G4)))</f>
         <v/>
@@ -2321,7 +2329,11 @@
         <f>IF(H5="TT","TRABAJO TERMINADO",IF(H5="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I5" s="7">
         <f>IF(B5="", G5, IF(G5="", LEFT(B5,45), IF(45-LEN(G5)-2&lt;=0, G5, LEFT(B5,45-LEN(G5)-2)&amp;", "&amp;G5)))</f>
         <v/>
@@ -2372,7 +2384,11 @@
         <f>IF(H6="TT","TRABAJO TERMINADO",IF(H6="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I6" s="7">
         <f>IF(B6="", G6, IF(G6="", LEFT(B6,45), IF(45-LEN(G6)-2&lt;=0, G6, LEFT(B6,45-LEN(G6)-2)&amp;", "&amp;G6)))</f>
         <v/>
@@ -2423,7 +2439,11 @@
         <f>IF(H7="TT","TRABAJO TERMINADO",IF(H7="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I7" s="7">
         <f>IF(B7="", G7, IF(G7="", LEFT(B7,45), IF(45-LEN(G7)-2&lt;=0, G7, LEFT(B7,45-LEN(G7)-2)&amp;", "&amp;G7)))</f>
         <v/>
@@ -2474,7 +2494,11 @@
         <f>IF(H8="TT","TRABAJO TERMINADO",IF(H8="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="I8" s="7">
         <f>IF(B8="", G8, IF(G8="", LEFT(B8,45), IF(45-LEN(G8)-2&lt;=0, G8, LEFT(B8,45-LEN(G8)-2)&amp;", "&amp;G8)))</f>
         <v/>
@@ -2483,7 +2507,11 @@
         <f>IF(H8="MI","NO REALIZADO " &amp; B8 &amp; " EN " &amp; C8 &amp; IF(K8&lt;&gt;""," " &amp; K8,""),IF(H8="TT","SE REALIZA " &amp; B8 &amp; " EN " &amp; C8 &amp; IF(K8&lt;&gt;""," " &amp; K8,""),""))</f>
         <v/>
       </c>
-      <c r="K8" s="4" t="n"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>SE SUSPENDE, BOMBA FUERA DE SERVICIO</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>ASUB</t>
@@ -2525,7 +2553,11 @@
         <f>IF(H9="TT","TRABAJO TERMINADO",IF(H9="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I9" s="7">
         <f>IF(B9="", G9, IF(G9="", LEFT(B9,45), IF(45-LEN(G9)-2&lt;=0, G9, LEFT(B9,45-LEN(G9)-2)&amp;", "&amp;G9)))</f>
         <v/>
@@ -2534,7 +2566,11 @@
         <f>IF(H9="MI","NO REALIZADO " &amp; B9 &amp; " EN " &amp; C9 &amp; IF(K9&lt;&gt;""," " &amp; K9,""),IF(H9="TT","SE REALIZA " &amp; B9 &amp; " EN " &amp; C9 &amp; IF(K9&lt;&gt;""," " &amp; K9,""),""))</f>
         <v/>
       </c>
-      <c r="K9" s="4" t="n"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Instrumentado</t>
+        </is>
+      </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -2576,7 +2612,11 @@
         <f>IF(H10="TT","TRABAJO TERMINADO",IF(H10="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I10" s="7">
         <f>IF(B10="", G10, IF(G10="", LEFT(B10,45), IF(45-LEN(G10)-2&lt;=0, G10, LEFT(B10,45-LEN(G10)-2)&amp;", "&amp;G10)))</f>
         <v/>
@@ -2627,7 +2667,11 @@
         <f>IF(H11="TT","TRABAJO TERMINADO",IF(H11="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="I11" s="7">
         <f>IF(B11="", G11, IF(G11="", LEFT(B11,45), IF(45-LEN(G11)-2&lt;=0, G11, LEFT(B11,45-LEN(G11)-2)&amp;", "&amp;G11)))</f>
         <v/>
@@ -2636,7 +2680,11 @@
         <f>IF(H11="MI","NO REALIZADO " &amp; B11 &amp; " EN " &amp; C11 &amp; IF(K11&lt;&gt;""," " &amp; K11,""),IF(H11="TT","SE REALIZA " &amp; B11 &amp; " EN " &amp; C11 &amp; IF(K11&lt;&gt;""," " &amp; K11,""),""))</f>
         <v/>
       </c>
-      <c r="K11" s="4" t="n"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>SE SUSPENDE PUNTO OBSTRUIDO A LOS 27,088m</t>
+        </is>
+      </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -2678,7 +2726,11 @@
         <f>IF(H12="TT","TRABAJO TERMINADO",IF(H12="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I12" s="7">
         <f>IF(B12="", G12, IF(G12="", LEFT(B12,45), IF(45-LEN(G12)-2&lt;=0, G12, LEFT(B12,45-LEN(G12)-2)&amp;", "&amp;G12)))</f>
         <v/>
@@ -2729,7 +2781,11 @@
         <f>IF(H13="TT","TRABAJO TERMINADO",IF(H13="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I13" s="7">
         <f>IF(B13="", G13, IF(G13="", LEFT(B13,45), IF(45-LEN(G13)-2&lt;=0, G13, LEFT(B13,45-LEN(G13)-2)&amp;", "&amp;G13)))</f>
         <v/>
@@ -2780,7 +2836,11 @@
         <f>IF(H14="TT","TRABAJO TERMINADO",IF(H14="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I14" s="7">
         <f>IF(B14="", G14, IF(G14="", LEFT(B14,45), IF(45-LEN(G14)-2&lt;=0, G14, LEFT(B14,45-LEN(G14)-2)&amp;", "&amp;G14)))</f>
         <v/>
@@ -2789,7 +2849,11 @@
         <f>IF(H14="MI","NO REALIZADO " &amp; B14 &amp; " EN " &amp; C14 &amp; IF(K14&lt;&gt;""," " &amp; K14,""),IF(H14="TT","SE REALIZA " &amp; B14 &amp; " EN " &amp; C14 &amp; IF(K14&lt;&gt;""," " &amp; K14,""),""))</f>
         <v/>
       </c>
-      <c r="K14" s="4" t="n"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>CALIDAD DE ENERO 2024 CON VIDEOINSPECCIÓN</t>
+        </is>
+      </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -2842,7 +2906,8 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>3 PERSONAS Y TRIPODE Y 2 YEGUA (POZ Y TRIPODE) PORTEZUELO</t>
+          <t>3 PERSONAS Y TRIPODE Y 2 YEGUA (POZ Y TRIPODE) PORTEZUELO
+SE SUSPENDE, CINTA POZOMETRO SE PEGA CON PARED DEL TUBO</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -2886,7 +2951,11 @@
         <f>IF(H16="TT","TRABAJO TERMINADO",IF(H16="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I16" s="7">
         <f>IF(B16="", G16, IF(G16="", LEFT(B16,45), IF(45-LEN(G16)-2&lt;=0, G16, LEFT(B16,45-LEN(G16)-2)&amp;", "&amp;G16)))</f>
         <v/>
@@ -2937,7 +3006,11 @@
         <f>IF(H17="TT","TRABAJO TERMINADO",IF(H17="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I17" s="7">
         <f>IF(B17="", G17, IF(G17="", LEFT(B17,45), IF(45-LEN(G17)-2&lt;=0, G17, LEFT(B17,45-LEN(G17)-2)&amp;", "&amp;G17)))</f>
         <v/>
@@ -2988,7 +3061,11 @@
         <f>IF(H18="TT","TRABAJO TERMINADO",IF(H18="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="I18" s="7">
         <f>IF(B18="", G18, IF(G18="", LEFT(B18,45), IF(45-LEN(G18)-2&lt;=0, G18, LEFT(B18,45-LEN(G18)-2)&amp;", "&amp;G18)))</f>
         <v/>
@@ -2997,7 +3074,11 @@
         <f>IF(H18="MI","NO REALIZADO " &amp; B18 &amp; " EN " &amp; C18 &amp; IF(K18&lt;&gt;""," " &amp; K18,""),IF(H18="TT","SE REALIZA " &amp; B18 &amp; " EN " &amp; C18 &amp; IF(K18&lt;&gt;""," " &amp; K18,""),""))</f>
         <v/>
       </c>
-      <c r="K18" s="4" t="n"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>TIEMPO LÍMITE PARA TRABAJOS FUERA DE FAENA</t>
+        </is>
+      </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3039,7 +3120,11 @@
         <f>IF(H19="TT","TRABAJO TERMINADO",IF(H19="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I19" s="7">
         <f>IF(B19="", G19, IF(G19="", LEFT(B19,45), IF(45-LEN(G19)-2&lt;=0, G19, LEFT(B19,45-LEN(G19)-2)&amp;", "&amp;G19)))</f>
         <v/>
@@ -3048,7 +3133,13 @@
         <f>IF(H19="MI","NO REALIZADO " &amp; B19 &amp; " EN " &amp; C19 &amp; IF(K19&lt;&gt;""," " &amp; K19,""),IF(H19="TT","SE REALIZA " &amp; B19 &amp; " EN " &amp; C19 &amp; IF(K19&lt;&gt;""," " &amp; K19,""),""))</f>
         <v/>
       </c>
-      <c r="K19" s="4" t="n"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>gtam instruimnentado
+Hito 54 carabineros 
+Calidad de aguas trimestral</t>
+        </is>
+      </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3090,7 +3181,11 @@
         <f>IF(H20="TT","TRABAJO TERMINADO",IF(H20="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I20" s="7">
         <f>IF(B20="", G20, IF(G20="", LEFT(B20,45), IF(45-LEN(G20)-2&lt;=0, G20, LEFT(B20,45-LEN(G20)-2)&amp;", "&amp;G20)))</f>
         <v/>
@@ -3099,7 +3194,11 @@
         <f>IF(H20="MI","NO REALIZADO " &amp; B20 &amp; " EN " &amp; C20 &amp; IF(K20&lt;&gt;""," " &amp; K20,""),IF(H20="TT","SE REALIZA " &amp; B20 &amp; " EN " &amp; C20 &amp; IF(K20&lt;&gt;""," " &amp; K20,""),""))</f>
         <v/>
       </c>
-      <c r="K20" s="4" t="n"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Instrumentalizado</t>
+        </is>
+      </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3141,7 +3240,11 @@
         <f>IF(H21="TT","TRABAJO TERMINADO",IF(H21="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I21" s="7">
         <f>IF(B21="", G21, IF(G21="", LEFT(B21,45), IF(45-LEN(G21)-2&lt;=0, G21, LEFT(B21,45-LEN(G21)-2)&amp;", "&amp;G21)))</f>
         <v/>
@@ -3150,7 +3253,13 @@
         <f>IF(H21="MI","NO REALIZADO " &amp; B21 &amp; " EN " &amp; C21 &amp; IF(K21&lt;&gt;""," " &amp; K21,""),IF(H21="TT","SE REALIZA " &amp; B21 &amp; " EN " &amp; C21 &amp; IF(K21&lt;&gt;""," " &amp; K21,""),""))</f>
         <v/>
       </c>
-      <c r="K21" s="4" t="n"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>gtam instruimnentado
+Hito 54 carabineros 
+Calidad de aguas trimestral</t>
+        </is>
+      </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3192,7 +3301,11 @@
         <f>IF(H22="TT","TRABAJO TERMINADO",IF(H22="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="I22" s="7">
         <f>IF(B22="", G22, IF(G22="", LEFT(B22,45), IF(45-LEN(G22)-2&lt;=0, G22, LEFT(B22,45-LEN(G22)-2)&amp;", "&amp;G22)))</f>
         <v/>
@@ -3201,7 +3314,11 @@
         <f>IF(H22="MI","NO REALIZADO " &amp; B22 &amp; " EN " &amp; C22 &amp; IF(K22&lt;&gt;""," " &amp; K22,""),IF(H22="TT","SE REALIZA " &amp; B22 &amp; " EN " &amp; C22 &amp; IF(K22&lt;&gt;""," " &amp; K22,""),""))</f>
         <v/>
       </c>
-      <c r="K22" s="4" t="n"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>TIEMPO LÍMITE PARA TRABAJOS FUERA DE FAENA</t>
+        </is>
+      </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3243,7 +3360,11 @@
         <f>IF(H23="TT","TRABAJO TERMINADO",IF(H23="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="I23" s="7">
         <f>IF(B23="", G23, IF(G23="", LEFT(B23,45), IF(45-LEN(G23)-2&lt;=0, G23, LEFT(B23,45-LEN(G23)-2)&amp;", "&amp;G23)))</f>
         <v/>
@@ -3252,7 +3373,11 @@
         <f>IF(H23="MI","NO REALIZADO " &amp; B23 &amp; " EN " &amp; C23 &amp; IF(K23&lt;&gt;""," " &amp; K23,""),IF(H23="TT","SE REALIZA " &amp; B23 &amp; " EN " &amp; C23 &amp; IF(K23&lt;&gt;""," " &amp; K23,""),""))</f>
         <v/>
       </c>
-      <c r="K23" s="4" t="n"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>TIEMPO LÍMITE PARA TRABAJOS FUERA DE FAENA</t>
+        </is>
+      </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3294,7 +3419,11 @@
         <f>IF(H24="TT","TRABAJO TERMINADO",IF(H24="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I24" s="7">
         <f>IF(B24="", G24, IF(G24="", LEFT(B24,45), IF(45-LEN(G24)-2&lt;=0, G24, LEFT(B24,45-LEN(G24)-2)&amp;", "&amp;G24)))</f>
         <v/>
@@ -3303,7 +3432,11 @@
         <f>IF(H24="MI","NO REALIZADO " &amp; B24 &amp; " EN " &amp; C24 &amp; IF(K24&lt;&gt;""," " &amp; K24,""),IF(H24="TT","SE REALIZA " &amp; B24 &amp; " EN " &amp; C24 &amp; IF(K24&lt;&gt;""," " &amp; K24,""),""))</f>
         <v/>
       </c>
-      <c r="K24" s="4" t="n"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>hito 54 Carabineros</t>
+        </is>
+      </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3345,7 +3478,11 @@
         <f>IF(H25="TT","TRABAJO TERMINADO",IF(H25="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I25" s="7">
         <f>IF(B25="", G25, IF(G25="", LEFT(B25,45), IF(45-LEN(G25)-2&lt;=0, G25, LEFT(B25,45-LEN(G25)-2)&amp;", "&amp;G25)))</f>
         <v/>
@@ -3354,7 +3491,13 @@
         <f>IF(H25="MI","NO REALIZADO " &amp; B25 &amp; " EN " &amp; C25 &amp; IF(K25&lt;&gt;""," " &amp; K25,""),IF(H25="TT","SE REALIZA " &amp; B25 &amp; " EN " &amp; C25 &amp; IF(K25&lt;&gt;""," " &amp; K25,""),""))</f>
         <v/>
       </c>
-      <c r="K25" s="4" t="n"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>gtam instruimnentado
+Hito 54 carabineros 
+Calidad de aguas trimestral</t>
+        </is>
+      </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3396,7 +3539,11 @@
         <f>IF(H26="TT","TRABAJO TERMINADO",IF(H26="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I26" s="7">
         <f>IF(B26="", G26, IF(G26="", LEFT(B26,45), IF(45-LEN(G26)-2&lt;=0, G26, LEFT(B26,45-LEN(G26)-2)&amp;", "&amp;G26)))</f>
         <v/>
@@ -3447,7 +3594,11 @@
         <f>IF(H27="TT","TRABAJO TERMINADO",IF(H27="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I27" s="7">
         <f>IF(B27="", G27, IF(G27="", LEFT(B27,45), IF(45-LEN(G27)-2&lt;=0, G27, LEFT(B27,45-LEN(G27)-2)&amp;", "&amp;G27)))</f>
         <v/>
@@ -3498,7 +3649,11 @@
         <f>IF(H28="TT","TRABAJO TERMINADO",IF(H28="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I28" s="7">
         <f>IF(B28="", G28, IF(G28="", LEFT(B28,45), IF(45-LEN(G28)-2&lt;=0, G28, LEFT(B28,45-LEN(G28)-2)&amp;", "&amp;G28)))</f>
         <v/>
@@ -3507,7 +3662,11 @@
         <f>IF(H28="MI","NO REALIZADO " &amp; B28 &amp; " EN " &amp; C28 &amp; IF(K28&lt;&gt;""," " &amp; K28,""),IF(H28="TT","SE REALIZA " &amp; B28 &amp; " EN " &amp; C28 &amp; IF(K28&lt;&gt;""," " &amp; K28,""),""))</f>
         <v/>
       </c>
-      <c r="K28" s="4" t="n"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Instrumentado</t>
+        </is>
+      </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3804,7 +3963,11 @@
         <f>IF(H34="TT","TRABAJO TERMINADO",IF(H34="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I34" s="7">
         <f>IF(B34="", G34, IF(G34="", LEFT(B34,45), IF(45-LEN(G34)-2&lt;=0, G34, LEFT(B34,45-LEN(G34)-2)&amp;", "&amp;G34)))</f>
         <v/>
@@ -3855,7 +4018,11 @@
         <f>IF(H35="TT","TRABAJO TERMINADO",IF(H35="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I35" s="7">
         <f>IF(B35="", G35, IF(G35="", LEFT(B35,45), IF(45-LEN(G35)-2&lt;=0, G35, LEFT(B35,45-LEN(G35)-2)&amp;", "&amp;G35)))</f>
         <v/>
@@ -3906,7 +4073,11 @@
         <f>IF(H36="TT","TRABAJO TERMINADO",IF(H36="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I36" s="7">
         <f>IF(B36="", G36, IF(G36="", LEFT(B36,45), IF(45-LEN(G36)-2&lt;=0, G36, LEFT(B36,45-LEN(G36)-2)&amp;", "&amp;G36)))</f>
         <v/>
@@ -3957,7 +4128,11 @@
         <f>IF(H37="TT","TRABAJO TERMINADO",IF(H37="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I37" s="7">
         <f>IF(B37="", G37, IF(G37="", LEFT(B37,45), IF(45-LEN(G37)-2&lt;=0, G37, LEFT(B37,45-LEN(G37)-2)&amp;", "&amp;G37)))</f>
         <v/>
@@ -4008,7 +4183,11 @@
         <f>IF(H38="TT","TRABAJO TERMINADO",IF(H38="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I38" s="7">
         <f>IF(B38="", G38, IF(G38="", LEFT(B38,45), IF(45-LEN(G38)-2&lt;=0, G38, LEFT(B38,45-LEN(G38)-2)&amp;", "&amp;G38)))</f>
         <v/>
@@ -4059,7 +4238,11 @@
         <f>IF(H39="TT","TRABAJO TERMINADO",IF(H39="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I39" s="7">
         <f>IF(B39="", G39, IF(G39="", LEFT(B39,45), IF(45-LEN(G39)-2&lt;=0, G39, LEFT(B39,45-LEN(G39)-2)&amp;", "&amp;G39)))</f>
         <v/>
@@ -4110,7 +4293,11 @@
         <f>IF(H40="TT","TRABAJO TERMINADO",IF(H40="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I40" s="7">
         <f>IF(B40="", G40, IF(G40="", LEFT(B40,45), IF(45-LEN(G40)-2&lt;=0, G40, LEFT(B40,45-LEN(G40)-2)&amp;", "&amp;G40)))</f>
         <v/>
@@ -4161,7 +4348,11 @@
         <f>IF(H41="TT","TRABAJO TERMINADO",IF(H41="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I41" s="7">
         <f>IF(B41="", G41, IF(G41="", LEFT(B41,45), IF(45-LEN(G41)-2&lt;=0, G41, LEFT(B41,45-LEN(G41)-2)&amp;", "&amp;G41)))</f>
         <v/>
@@ -4212,7 +4403,11 @@
         <f>IF(H42="TT","TRABAJO TERMINADO",IF(H42="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I42" s="7">
         <f>IF(B42="", G42, IF(G42="", LEFT(B42,45), IF(45-LEN(G42)-2&lt;=0, G42, LEFT(B42,45-LEN(G42)-2)&amp;", "&amp;G42)))</f>
         <v/>
@@ -4263,7 +4458,11 @@
         <f>IF(H43="TT","TRABAJO TERMINADO",IF(H43="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I43" s="7">
         <f>IF(B43="", G43, IF(G43="", LEFT(B43,45), IF(45-LEN(G43)-2&lt;=0, G43, LEFT(B43,45-LEN(G43)-2)&amp;", "&amp;G43)))</f>
         <v/>
@@ -4314,7 +4513,11 @@
         <f>IF(H44="TT","TRABAJO TERMINADO",IF(H44="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I44" s="7">
         <f>IF(B44="", G44, IF(G44="", LEFT(B44,45), IF(45-LEN(G44)-2&lt;=0, G44, LEFT(B44,45-LEN(G44)-2)&amp;", "&amp;G44)))</f>
         <v/>
@@ -4365,7 +4568,11 @@
         <f>IF(H45="TT","TRABAJO TERMINADO",IF(H45="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I45" s="7">
         <f>IF(B45="", G45, IF(G45="", LEFT(B45,45), IF(45-LEN(G45)-2&lt;=0, G45, LEFT(B45,45-LEN(G45)-2)&amp;", "&amp;G45)))</f>
         <v/>
@@ -4416,7 +4623,11 @@
         <f>IF(H46="TT","TRABAJO TERMINADO",IF(H46="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I46" s="7">
         <f>IF(B46="", G46, IF(G46="", LEFT(B46,45), IF(45-LEN(G46)-2&lt;=0, G46, LEFT(B46,45-LEN(G46)-2)&amp;", "&amp;G46)))</f>
         <v/>
@@ -4467,7 +4678,11 @@
         <f>IF(H47="TT","TRABAJO TERMINADO",IF(H47="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I47" s="7">
         <f>IF(B47="", G47, IF(G47="", LEFT(B47,45), IF(45-LEN(G47)-2&lt;=0, G47, LEFT(B47,45-LEN(G47)-2)&amp;", "&amp;G47)))</f>
         <v/>
@@ -4518,7 +4733,11 @@
         <f>IF(H48="TT","TRABAJO TERMINADO",IF(H48="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I48" s="7">
         <f>IF(B48="", G48, IF(G48="", LEFT(B48,45), IF(45-LEN(G48)-2&lt;=0, G48, LEFT(B48,45-LEN(G48)-2)&amp;", "&amp;G48)))</f>
         <v/>
@@ -4569,7 +4788,11 @@
         <f>IF(H49="TT","TRABAJO TERMINADO",IF(H49="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I49" s="7">
         <f>IF(B49="", G49, IF(G49="", LEFT(B49,45), IF(45-LEN(G49)-2&lt;=0, G49, LEFT(B49,45-LEN(G49)-2)&amp;", "&amp;G49)))</f>
         <v/>
@@ -4620,7 +4843,11 @@
         <f>IF(H50="TT","TRABAJO TERMINADO",IF(H50="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I50" s="7">
         <f>IF(B50="", G50, IF(G50="", LEFT(B50,45), IF(45-LEN(G50)-2&lt;=0, G50, LEFT(B50,45-LEN(G50)-2)&amp;", "&amp;G50)))</f>
         <v/>
@@ -4671,7 +4898,11 @@
         <f>IF(H51="TT","TRABAJO TERMINADO",IF(H51="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I51" s="7">
         <f>IF(B51="", G51, IF(G51="", LEFT(B51,45), IF(45-LEN(G51)-2&lt;=0, G51, LEFT(B51,45-LEN(G51)-2)&amp;", "&amp;G51)))</f>
         <v/>
@@ -4773,7 +5004,11 @@
         <f>IF(H53="TT","TRABAJO TERMINADO",IF(H53="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I53" s="7">
         <f>IF(B53="", G53, IF(G53="", LEFT(B53,45), IF(45-LEN(G53)-2&lt;=0, G53, LEFT(B53,45-LEN(G53)-2)&amp;", "&amp;G53)))</f>
         <v/>
@@ -4824,7 +5059,11 @@
         <f>IF(H54="TT","TRABAJO TERMINADO",IF(H54="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I54" s="7">
         <f>IF(B54="", G54, IF(G54="", LEFT(B54,45), IF(45-LEN(G54)-2&lt;=0, G54, LEFT(B54,45-LEN(G54)-2)&amp;", "&amp;G54)))</f>
         <v/>
@@ -4875,7 +5114,11 @@
         <f>IF(H55="TT","TRABAJO TERMINADO",IF(H55="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I55" s="7">
         <f>IF(B55="", G55, IF(G55="", LEFT(B55,45), IF(45-LEN(G55)-2&lt;=0, G55, LEFT(B55,45-LEN(G55)-2)&amp;", "&amp;G55)))</f>
         <v/>
@@ -4926,7 +5169,11 @@
         <f>IF(H56="TT","TRABAJO TERMINADO",IF(H56="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I56" s="7">
         <f>IF(B56="", G56, IF(G56="", LEFT(B56,45), IF(45-LEN(G56)-2&lt;=0, G56, LEFT(B56,45-LEN(G56)-2)&amp;", "&amp;G56)))</f>
         <v/>
@@ -5028,7 +5275,11 @@
         <f>IF(H58="TT","TRABAJO TERMINADO",IF(H58="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I58" s="7">
         <f>IF(B58="", G58, IF(G58="", LEFT(B58,45), IF(45-LEN(G58)-2&lt;=0, G58, LEFT(B58,45-LEN(G58)-2)&amp;", "&amp;G58)))</f>
         <v/>
@@ -5079,7 +5330,11 @@
         <f>IF(H59="TT","TRABAJO TERMINADO",IF(H59="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I59" s="7">
         <f>IF(B59="", G59, IF(G59="", LEFT(B59,45), IF(45-LEN(G59)-2&lt;=0, G59, LEFT(B59,45-LEN(G59)-2)&amp;", "&amp;G59)))</f>
         <v/>
@@ -5130,7 +5385,11 @@
         <f>IF(H60="TT","TRABAJO TERMINADO",IF(H60="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="I60" s="7">
         <f>IF(B60="", G60, IF(G60="", LEFT(B60,45), IF(45-LEN(G60)-2&lt;=0, G60, LEFT(B60,45-LEN(G60)-2)&amp;", "&amp;G60)))</f>
         <v/>
@@ -5139,7 +5398,11 @@
         <f>IF(H60="MI","NO REALIZADO " &amp; B60 &amp; " EN " &amp; C60 &amp; IF(K60&lt;&gt;""," " &amp; K60,""),IF(H60="TT","SE REALIZA " &amp; B60 &amp; " EN " &amp; C60 &amp; IF(K60&lt;&gt;""," " &amp; K60,""),""))</f>
         <v/>
       </c>
-      <c r="K60" s="4" t="n"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>PUNTO DE MONITOREO FUERA DE SERVICIO</t>
+        </is>
+      </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
           <t>ASUB</t>
@@ -5181,7 +5444,11 @@
         <f>IF(H61="TT","TRABAJO TERMINADO",IF(H61="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I61" s="7">
         <f>IF(B61="", G61, IF(G61="", LEFT(B61,45), IF(45-LEN(G61)-2&lt;=0, G61, LEFT(B61,45-LEN(G61)-2)&amp;", "&amp;G61)))</f>
         <v/>
@@ -5190,7 +5457,12 @@
         <f>IF(H61="MI","NO REALIZADO " &amp; B61 &amp; " EN " &amp; C61 &amp; IF(K61&lt;&gt;""," " &amp; K61,""),IF(H61="TT","SE REALIZA " &amp; B61 &amp; " EN " &amp; C61 &amp; IF(K61&lt;&gt;""," " &amp; K61,""),""))</f>
         <v/>
       </c>
-      <c r="K61" s="4" t="n"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Lo realiza la GTAM instrumentado
+Calidad de aguas trimestral</t>
+        </is>
+      </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -5232,7 +5504,11 @@
         <f>IF(H62="TT","TRABAJO TERMINADO",IF(H62="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I62" s="7">
         <f>IF(B62="", G62, IF(G62="", LEFT(B62,45), IF(45-LEN(G62)-2&lt;=0, G62, LEFT(B62,45-LEN(G62)-2)&amp;", "&amp;G62)))</f>
         <v/>
@@ -5241,7 +5517,11 @@
         <f>IF(H62="MI","NO REALIZADO " &amp; B62 &amp; " EN " &amp; C62 &amp; IF(K62&lt;&gt;""," " &amp; K62,""),IF(H62="TT","SE REALIZA " &amp; B62 &amp; " EN " &amp; C62 &amp; IF(K62&lt;&gt;""," " &amp; K62,""),""))</f>
         <v/>
       </c>
-      <c r="K62" s="4" t="n"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>CAMBIO DE FRECUENCIA A PARTIR DE SEPTIEMBRE 2025 X CMDIC DE MENSUAL A TRIMESTRAL</t>
+        </is>
+      </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -5495,7 +5775,11 @@
         <f>IF(H67="TT","TRABAJO TERMINADO",IF(H67="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I67" s="7">
         <f>IF(B67="", G67, IF(G67="", LEFT(B67,45), IF(45-LEN(G67)-2&lt;=0, G67, LEFT(B67,45-LEN(G67)-2)&amp;", "&amp;G67)))</f>
         <v/>
@@ -5852,7 +6136,11 @@
         <f>IF(H74="TT","TRABAJO TERMINADO",IF(H74="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I74" s="7">
         <f>IF(B74="", G74, IF(G74="", LEFT(B74,45), IF(45-LEN(G74)-2&lt;=0, G74, LEFT(B74,45-LEN(G74)-2)&amp;", "&amp;G74)))</f>
         <v/>
@@ -5912,7 +6200,11 @@
         <f>IF(H75="MI","NO REALIZADO " &amp; B75 &amp; " EN " &amp; C75 &amp; IF(K75&lt;&gt;""," " &amp; K75,""),IF(H75="TT","SE REALIZA " &amp; B75 &amp; " EN " &amp; C75 &amp; IF(K75&lt;&gt;""," " &amp; K75,""),""))</f>
         <v/>
       </c>
-      <c r="K75" s="4" t="n"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>REPROGRAMADO POR PRIORIDAD ENVÍO DE MUESTRAS</t>
+        </is>
+      </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
           <t>ASUB</t>
@@ -5954,7 +6246,11 @@
         <f>IF(H76="TT","TRABAJO TERMINADO",IF(H76="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I76" s="7">
         <f>IF(B76="", G76, IF(G76="", LEFT(B76,45), IF(45-LEN(G76)-2&lt;=0, G76, LEFT(B76,45-LEN(G76)-2)&amp;", "&amp;G76)))</f>
         <v/>
@@ -6014,7 +6310,11 @@
         <f>IF(H77="MI","NO REALIZADO " &amp; B77 &amp; " EN " &amp; C77 &amp; IF(K77&lt;&gt;""," " &amp; K77,""),IF(H77="TT","SE REALIZA " &amp; B77 &amp; " EN " &amp; C77 &amp; IF(K77&lt;&gt;""," " &amp; K77,""),""))</f>
         <v/>
       </c>
-      <c r="K77" s="4" t="n"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>REPROGRAMADO POR PRIORIDAD ENVÍO DE MUESTRAS</t>
+        </is>
+      </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
           <t>NF</t>
@@ -6107,7 +6407,11 @@
         <f>IF(H79="TT","TRABAJO TERMINADO",IF(H79="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I79" s="7">
         <f>IF(B79="", G79, IF(G79="", LEFT(B79,45), IF(45-LEN(G79)-2&lt;=0, G79, LEFT(B79,45-LEN(G79)-2)&amp;", "&amp;G79)))</f>
         <v/>
@@ -6158,7 +6462,11 @@
         <f>IF(H80="TT","TRABAJO TERMINADO",IF(H80="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I80" s="7">
         <f>IF(B80="", G80, IF(G80="", LEFT(B80,45), IF(45-LEN(G80)-2&lt;=0, G80, LEFT(B80,45-LEN(G80)-2)&amp;", "&amp;G80)))</f>
         <v/>
@@ -6209,7 +6517,11 @@
         <f>IF(H81="TT","TRABAJO TERMINADO",IF(H81="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I81" s="7">
         <f>IF(B81="", G81, IF(G81="", LEFT(B81,45), IF(45-LEN(G81)-2&lt;=0, G81, LEFT(B81,45-LEN(G81)-2)&amp;", "&amp;G81)))</f>
         <v/>
@@ -6269,7 +6581,11 @@
         <f>IF(H82="MI","NO REALIZADO " &amp; B82 &amp; " EN " &amp; C82 &amp; IF(K82&lt;&gt;""," " &amp; K82,""),IF(H82="TT","SE REALIZA " &amp; B82 &amp; " EN " &amp; C82 &amp; IF(K82&lt;&gt;""," " &amp; K82,""),""))</f>
         <v/>
       </c>
-      <c r="K82" s="4" t="n"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>SE SUSPENDE POR PRESENCIA DE RODADOS</t>
+        </is>
+      </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
           <t>CAUDAL</t>
@@ -6696,7 +7012,11 @@
         <f>IF(H90="TT","TRABAJO TERMINADO",IF(H90="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I90" s="7">
         <f>IF(B90="", G90, IF(G90="", LEFT(B90,45), IF(45-LEN(G90)-2&lt;=0, G90, LEFT(B90,45-LEN(G90)-2)&amp;", "&amp;G90)))</f>
         <v/>
@@ -6705,7 +7025,11 @@
         <f>IF(H90="MI","NO REALIZADO " &amp; B90 &amp; " EN " &amp; C90 &amp; IF(K90&lt;&gt;""," " &amp; K90,""),IF(H90="TT","SE REALIZA " &amp; B90 &amp; " EN " &amp; C90 &amp; IF(K90&lt;&gt;""," " &amp; K90,""),""))</f>
         <v/>
       </c>
-      <c r="K90" s="4" t="n"/>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>pedir carry all</t>
+        </is>
+      </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
           <t>ASUP</t>
@@ -6747,7 +7071,11 @@
         <f>IF(H91="TT","TRABAJO TERMINADO",IF(H91="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H91" s="6" t="inlineStr"/>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I91" s="7">
         <f>IF(B91="", G91, IF(G91="", LEFT(B91,45), IF(45-LEN(G91)-2&lt;=0, G91, LEFT(B91,45-LEN(G91)-2)&amp;", "&amp;G91)))</f>
         <v/>
@@ -6798,7 +7126,11 @@
         <f>IF(H92="TT","TRABAJO TERMINADO",IF(H92="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I92" s="7">
         <f>IF(B92="", G92, IF(G92="", LEFT(B92,45), IF(45-LEN(G92)-2&lt;=0, G92, LEFT(B92,45-LEN(G92)-2)&amp;", "&amp;G92)))</f>
         <v/>
@@ -6807,7 +7139,11 @@
         <f>IF(H92="MI","NO REALIZADO " &amp; B92 &amp; " EN " &amp; C92 &amp; IF(K92&lt;&gt;""," " &amp; K92,""),IF(H92="TT","SE REALIZA " &amp; B92 &amp; " EN " &amp; C92 &amp; IF(K92&lt;&gt;""," " &amp; K92,""),""))</f>
         <v/>
       </c>
-      <c r="K92" s="4" t="n"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>(dias lunespor solicitud CMDIC/ECOS)</t>
+        </is>
+      </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
           <t>ASUP</t>
@@ -7537,7 +7873,11 @@
         <f>IF(H8="TT","TRABAJO TERMINADO",IF(H8="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I8" s="7">
         <f>IF(B8="", G8, IF(G8="", LEFT(B8,45), IF(45-LEN(G8)-2&lt;=0, G8, LEFT(B8,45-LEN(G8)-2)&amp;", "&amp;G8)))</f>
         <v/>
@@ -7546,7 +7886,11 @@
         <f>IF(H8="MI","NO REALIZADO " &amp; B8 &amp; " EN " &amp; C8 &amp; IF(K8&lt;&gt;""," " &amp; K8,""),IF(H8="TT","SE REALIZA " &amp; B8 &amp; " EN " &amp; C8 &amp; IF(K8&lt;&gt;""," " &amp; K8,""),""))</f>
         <v/>
       </c>
-      <c r="K8" s="4" t="n"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>HoldingTime 20 hrs</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>AR</t>
@@ -7741,7 +8085,11 @@
         <f>IF(H12="TT","TRABAJO TERMINADO",IF(H12="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I12" s="7">
         <f>IF(B12="", G12, IF(G12="", LEFT(B12,45), IF(45-LEN(G12)-2&lt;=0, G12, LEFT(B12,45-LEN(G12)-2)&amp;", "&amp;G12)))</f>
         <v/>
@@ -7852,7 +8200,11 @@
         <f>IF(H14="MI","NO REALIZADO " &amp; B14 &amp; " EN " &amp; C14 &amp; IF(K14&lt;&gt;""," " &amp; K14,""),IF(H14="TT","SE REALIZA " &amp; B14 &amp; " EN " &amp; C14 &amp; IF(K14&lt;&gt;""," " &amp; K14,""),""))</f>
         <v/>
       </c>
-      <c r="K14" s="4" t="n"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>SE SUSPENDE POR PRESENCIA DE RODADOS</t>
+        </is>
+      </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>FOTOMETRO</t>
@@ -8557,7 +8909,11 @@
         <f>IF(H28="TT","TRABAJO TERMINADO",IF(H28="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I28" s="7">
         <f>IF(B28="", G28, IF(G28="", LEFT(B28,45), IF(45-LEN(G28)-2&lt;=0, G28, LEFT(B28,45-LEN(G28)-2)&amp;", "&amp;G28)))</f>
         <v/>
@@ -8566,7 +8922,11 @@
         <f>IF(H28="MI","NO REALIZADO " &amp; B28 &amp; " EN " &amp; C28 &amp; IF(K28&lt;&gt;""," " &amp; K28,""),IF(H28="TT","SE REALIZA " &amp; B28 &amp; " EN " &amp; C28 &amp; IF(K28&lt;&gt;""," " &amp; K28,""),""))</f>
         <v/>
       </c>
-      <c r="K28" s="4" t="n"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>HoldingTime 20 hrs</t>
+        </is>
+      </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
           <t>AR</t>
@@ -8659,7 +9019,11 @@
         <f>IF(H30="TT","TRABAJO TERMINADO",IF(H30="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I30" s="7">
         <f>IF(B30="", G30, IF(G30="", LEFT(B30,45), IF(45-LEN(G30)-2&lt;=0, G30, LEFT(B30,45-LEN(G30)-2)&amp;", "&amp;G30)))</f>
         <v/>
@@ -9129,7 +9493,11 @@
         <f>IF(H40="TT","TRABAJO TERMINADO",IF(H40="MI","TRABAJO NO TERMINADO",""))</f>
         <v/>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
       <c r="I40" s="7">
         <f>IF(B40="", G40, IF(G40="", LEFT(B40,45), IF(45-LEN(G40)-2&lt;=0, G40, LEFT(B40,45-LEN(G40)-2)&amp;", "&amp;G40)))</f>
         <v/>
